--- a/nursing/フォーマット/03_就労支援記録様式/10_アセスメント票.xlsx
+++ b/nursing/フォーマット/03_就労支援記録様式/10_アセスメント票.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,7 +33,9 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -43,12 +45,21 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
       <i val="1"/>
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0E7490"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFFAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,18 +100,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,10 +488,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -476,158 +501,289 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>アセスメント票（就労継続支援A型・B型・相談支援共通）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>アセスメントシート（就労支援・居宅介護・相談支援共通版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>アセスメント実施日：　　年　月　日　実施者：　　　　　　利用者氏名：　　　　　　（参加者：本人・家族・相談支援専門員・その他：　　　）</t>
+          <t>【実施タイミング】サービス開始前・個別支援計画見直し時・状況変化時。本人・家族等の参加のもと実施することが望ましい。ICF（国際生活機能分類）の視点を活用。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>【本人の意向・希望】</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
+          <t>【基本情報・実施状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>（どんな仕事・活動をしたいか。将来の希望。生活の希望。）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>【日常生活の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>利用者氏名</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>（様）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>生年月日・年齢</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日生（　歳）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>（起床・就寝時刻 / 食事・服薬の自己管理 / 清潔管理 / 外出・移動 / コミュニケーション能力）</t>
+          <t>利用するサービス種別</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>本人 / 家族（　）/ 相談支援専門員 / その他</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>【就労能力・作業能力】</t>
+          <t>【本人の意向・夢・将来の希望】（強みベースで記録）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>（作業の持続時間（　　h） / 集中力 / 体力・持久力 / 手先の器用さ / 指示理解力 / 協調性）</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>「どんな生活をしたいか」「何がやりたいか」「どんな仕事・活動をしてみたいか」を本人の言葉で記録。
+例）「自分で稼ぎたい」「料理を覚えたい」「一人暮らしがしたい」</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>【健康・医療の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>（現在の傷病 / 服薬状況 / 通院状況 / 精神状態の波 / 体調悪化の兆候・サイン）</t>
+          <t>【障害の状況・特性】（強みも含めて記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>障害の種別・程度・診断名。障害の特性（感覚過敏・パニック時の対応・得意な作業）。コミュニケーションの方法（話す/書く/絵/AAC等）。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>【支援のニーズ（本人・家族）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>（何を支援してほしいか。日常生活上の困りごと。就労上の困りごと。）</t>
+          <t>【健康・医療の状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>主傷病名・副傷病名・既往歴。通院状況・頻度・主治医名。服薬状況（種類・管理方法）。体調の波・悪化のサイン・てんかん発作の有無。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>【家族・住環境の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>（同居家族 / キーパーソン / 家族の支援状況 / 住居の状況）</t>
+          <t>【日常生活・ADLの状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>食事（自立/介助要）　排泄（自立/介助要）　入浴（自立/介助要）　着替え（自立/介助要）　移動（自立/車椅子/介助要）
+服薬管理（自立/支援要）　金銭管理（自立/支援要）　調理（自立/支援要）　掃除・洗濯（自立/支援要）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>【社会参加・日中活動の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>（現在の利用サービス / 余暇活動 / 地域との関係）</t>
+          <t>【就労・活動能力の状況】（就労系サービスのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>作業の持続時間（　h）　手先の器用さ（良好/普通/課題あり）　指示理解力（口頭/書面/実演で理解）
+集中力・体力・協調性・自己申告（体調悪化を自分で申し出られるか）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>【支援上の課題・優先事項】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>（アセスメントから見えた課題。個別支援計画の目標設定に向けた優先事項。）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">アセスメント実施者署名：　　　　　　　　　　　日付：　　年　月　日　確認者（サビ管）：　　　　　　　　</t>
+          <t>【社会参加・日中活動の状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>現在利用中のサービス（種別・事業所名・利用頻度）。地域・コミュニティとの関係。余暇活動・趣味。外出頻度・交通機関の利用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>【家族・住環境・支援体制の状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>同居家族・キーパーソン（氏名・続柄・連絡先・介護力）。住居形態（自宅/GH/施設）。バリアフリー状況。家族の介護力・支援意向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>【経済状況・制度利用状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>収入源（障害年金/就労賃金・工賃/生活保護/その他）。活用中の制度（障害者手帳・自立支援医療・成年後見等）。経済的な困難・課題。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>【本人・家族のニーズ（解決すべき課題）まとめ】</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>上記のアセスメントを踏まえて、支援の優先課題を箇条書きで整理する。
+① 　② 　③ 　④</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>【強みと活用できるリソース】（ストレングスベース）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="50" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>例）手先が器用で封入作業が得意。音楽が大好きで気持ちが安定する。家族のサポートが手厚い。主治医との関係が良好。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>【アセスメントから見えた支援の方向性】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>個別支援計画の目標・支援内容の方向性について整理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>アセスメント実施者署名：　　　　　　　　　　　（日付：　年　月　日）
+サービス管理責任者・確認者：　　　　　　　　（日付：　年　月　日）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="38">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
   </mergeCells>

--- a/nursing/フォーマット/03_就労支援記録様式/10_アセスメント票.xlsx
+++ b/nursing/フォーマット/03_就労支援記録様式/10_アセスメント票.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメント票" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメント" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,37 +26,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFDC2626"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <sz val="9"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -68,21 +68,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -91,38 +91,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,307 +508,327 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>アセスメントシート（就労支援・居宅介護・相談支援共通版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>アセスメントシート（就労支援・生活支援・心身機能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【実施タイミング】サービス開始前・個別支援計画見直し時・状況変化時。本人・家族等の参加のもと実施することが望ましい。ICF（国際生活機能分類）の視点を活用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>【基本情報・実施状況】</t>
-        </is>
-      </c>
-    </row>
+          <t>個別支援計画の前提となる情報収集。本人の強み（ストレングス）も把握</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>利用者氏名</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>実施日</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日</t>
-        </is>
-      </c>
+          <t>氏名 / 生年月日</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>生年月日・年齢</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日生（　歳）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>実施者</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>実施日 / 実施者</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>利用するサービス種別</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>参加者</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>本人 / 家族（　）/ 相談支援専門員 / その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>【本人の意向・夢・将来の希望】（強みベースで記録）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>「どんな生活をしたいか」「何がやりたいか」「どんな仕事・活動をしてみたいか」を本人の言葉で記録。
-例）「自分で稼ぎたい」「料理を覚えたい」「一人暮らしがしたい」</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>【障害の状況・特性】（強みも含めて記録）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>障害の種別・程度・診断名。障害の特性（感覚過敏・パニック時の対応・得意な作業）。コミュニケーションの方法（話す/書く/絵/AAC等）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>【健康・医療の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>主傷病名・副傷病名・既往歴。通院状況・頻度・主治医名。服薬状況（種類・管理方法）。体調の波・悪化のサイン・てんかん発作の有無。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>【日常生活・ADLの状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>食事（自立/介助要）　排泄（自立/介助要）　入浴（自立/介助要）　着替え（自立/介助要）　移動（自立/車椅子/介助要）
-服薬管理（自立/支援要）　金銭管理（自立/支援要）　調理（自立/支援要）　掃除・洗濯（自立/支援要）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>【就労・活動能力の状況】（就労系サービスのみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>作業の持続時間（　h）　手先の器用さ（良好/普通/課題あり）　指示理解力（口頭/書面/実演で理解）
-集中力・体力・協調性・自己申告（体調悪化を自分で申し出られるか）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>【社会参加・日中活動の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>現在利用中のサービス（種別・事業所名・利用頻度）。地域・コミュニティとの関係。余暇活動・趣味。外出頻度・交通機関の利用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>【家族・住環境・支援体制の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>同居家族・キーパーソン（氏名・続柄・連絡先・介護力）。住居形態（自宅/GH/施設）。バリアフリー状況。家族の介護力・支援意向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>【経済状況・制度利用状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="55" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>収入源（障害年金/就労賃金・工賃/生活保護/その他）。活用中の制度（障害者手帳・自立支援医療・成年後見等）。経済的な困難・課題。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>【本人・家族のニーズ（解決すべき課題）まとめ】</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>上記のアセスメントを踏まえて、支援の優先課題を箇条書きで整理する。
-① 　② 　③ 　④</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>【強みと活用できるリソース】（ストレングスベース）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="50" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>例）手先が器用で封入作業が得意。音楽が大好きで気持ちが安定する。家族のサポートが手厚い。主治医との関係が良好。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>【アセスメントから見えた支援の方向性】</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>個別支援計画の目標・支援内容の方向性について整理する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>アセスメント実施者署名：　　　　　　　　　　　（日付：　年　月　日）
-サービス管理責任者・確認者：　　　　　　　　（日付：　年　月　日）</t>
-        </is>
-      </c>
+          <t>情報源</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>□本人　□家族　□相談支援　□医療機関　□前事業所</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>1. 心身の状況・健康・服薬</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2. 日常生活（ADL/IADL）・生活リズム</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>3. コミュニケーション・対人関係</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>4. 作業能力・職業適性・就労経験</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>5. 本人の希望・強み（ストレングス）・興味関心</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>6. 支援上の課題とニーズの整理</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>※ できないことだけでなく「できること・好きなこと」を重視。本人参加で作成し、定期的に再アセスメントする。</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A21:H21"/>
+  <mergeCells count="15">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:H6"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="C5:H5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="C4:H4"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>